--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484843_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484843_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.121</v>
+        <v>6.478</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3756</v>
+        <v>6.7855</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2546</v>
+        <v>-0.3075</v>
       </c>
       <c r="G2" t="n">
         <v>5.5978</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0992</v>
+        <v>-0.7423</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8818</v>
+        <v>-0.4719</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2174</v>
+        <v>-0.2703</v>
       </c>
       <c r="V2" t="n">
         <v>2.1886</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>V. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8537</v>
+        <v>1.6351</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2629</v>
+        <v>4.7098</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5908</v>
+        <v>-3.0747</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0446</v>
+        <v>0.9984</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6425</v>
+        <v>-1.5261</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5979</v>
+        <v>2.5245</v>
       </c>
       <c r="J3" t="n">
-        <v>1.311</v>
+        <v>3.1723</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1465</v>
+        <v>1.1895</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1645</v>
+        <v>1.9828</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3556</v>
+        <v>-2.1738</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.789</v>
+        <v>-2.7156</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4334</v>
+        <v>0.5417</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>1.887</v>
+        <v>2.2644</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6531</v>
+        <v>-0.3634</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5937</v>
+        <v>-0.3112</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0595</v>
+        <v>-0.0522</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2452</v>
+        <v>-0.3208</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2452</v>
+        <v>2.7922</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. GALVEZ ARROYO</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2085</v>
+        <v>1.1427</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4948</v>
+        <v>0.7371</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.2863</v>
+        <v>0.4057</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9984</v>
+        <v>-0.0446</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5261</v>
+        <v>-0.6425</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5245</v>
+        <v>0.5979</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1723</v>
+        <v>1.311</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1895</v>
+        <v>1.1465</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9828</v>
+        <v>0.1645</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1738</v>
+        <v>-1.3556</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.7156</v>
+        <v>-1.789</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5417</v>
+        <v>0.4334</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2644</v>
+        <v>1.887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7901</v>
+        <v>-0.0579</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5262</v>
+        <v>0.0679</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2639</v>
+        <v>-0.1257</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3208</v>
+        <v>1.2452</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7922</v>
+        <v>1.2452</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5346</v>
+        <v>-1.3654</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.795</v>
+        <v>-1.9697</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2604</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5533</v>
@@ -844,13 +844,13 @@
         <v>1.3209</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.736</v>
+        <v>-0.5668</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1735</v>
+        <v>-0.3482</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5625</v>
+        <v>-0.2186</v>
       </c>
       <c r="V5" t="n">
         <v>0.3208</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1157</v>
+        <v>-2.111</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7212</v>
+        <v>-0.2139</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3944</v>
+        <v>-1.8971</v>
       </c>
       <c r="G6" t="n">
         <v>0.4658</v>
@@ -922,13 +922,13 @@
         <v>1.5096</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0346</v>
+        <v>-0.0299</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7055</v>
+        <v>-0.1981</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6708</v>
+        <v>0.1682</v>
       </c>
       <c r="V6" t="n">
         <v>-3.113</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1353</v>
+        <v>-2.3629</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0548</v>
+        <v>-0.1199</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1901</v>
+        <v>-2.243</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9747</v>
@@ -1000,13 +1000,13 @@
         <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2363</v>
+        <v>-0.4639</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2323</v>
+        <v>-0.407</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0041</v>
+        <v>-0.057</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8678</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0366</v>
+        <v>-2.4474</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7724</v>
+        <v>-1.4213</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2642</v>
+        <v>-1.0261</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6539</v>
@@ -1078,13 +1078,13 @@
         <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9488</v>
+        <v>-0.3596</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.2956</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3021</v>
+        <v>-0.064</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.643700000000001</v>
+        <v>-8.369899999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.4165</v>
+        <v>-7.1427</v>
       </c>
       <c r="F9" t="n">
         <v>-1.2272</v>
@@ -1156,10 +1156,10 @@
         <v>2.4531</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4732</v>
+        <v>-0.1994</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.585</v>
+        <v>-0.3112</v>
       </c>
       <c r="U9" t="n">
         <v>0.1118</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.2827</v>
+        <v>-7.4008</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4830000000000005</v>
+        <v>1.3649</v>
       </c>
       <c r="F10" t="n">
         <v>-8.765600000000001</v>
@@ -1204,7 +1204,7 @@
         <v>-3.5764</v>
       </c>
       <c r="I10" t="n">
-        <v>5.846000000000001</v>
+        <v>5.846</v>
       </c>
       <c r="J10" t="n">
         <v>12.8693</v>
@@ -1222,7 +1222,7 @@
         <v>-11.144</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5443</v>
+        <v>0.5442999999999999</v>
       </c>
       <c r="P10" t="n">
         <v>-4.717500000000001</v>
@@ -1234,13 +1234,13 @@
         <v>13.209</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.6651</v>
+        <v>-2.7832</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.1573</v>
+        <v>-2.2753</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5079</v>
+        <v>-0.5078</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1696</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.353999999999999</v>
+        <v>7.0705</v>
       </c>
       <c r="E11" t="n">
-        <v>7.4463</v>
+        <v>6.3745</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9077</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.9462</v>
@@ -1312,13 +1312,13 @@
         <v>3.0192</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4078</v>
+        <v>1.1244</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5401</v>
+        <v>0.4683</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8677</v>
+        <v>0.6561</v>
       </c>
       <c r="V11" t="n">
         <v>3.113</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.262</v>
+        <v>4.0407</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2955</v>
+        <v>1.1006</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9665</v>
+        <v>2.9401</v>
       </c>
       <c r="G12" t="n">
         <v>4.4437</v>
@@ -1390,13 +1390,13 @@
         <v>2.8305</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7618</v>
+        <v>0.5405</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2997</v>
+        <v>0.1049</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4621</v>
+        <v>0.4356</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4237</v>
+        <v>3.8051</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6433</v>
+        <v>3.1305</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7804</v>
+        <v>0.6746</v>
       </c>
       <c r="G13" t="n">
         <v>1.9087</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2963</v>
+        <v>0.0851</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.1595</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3504</v>
+        <v>0.2446</v>
       </c>
       <c r="V13" t="n">
         <v>1.2452</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1212</v>
+        <v>3.6432</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4207</v>
+        <v>3.8105</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2996</v>
+        <v>-0.1673</v>
       </c>
       <c r="G14" t="n">
         <v>3.6874</v>
@@ -1546,13 +1546,13 @@
         <v>1.5096</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8306</v>
+        <v>-0.3086</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.2569</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.184</v>
+        <v>-0.0517</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2452</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7884</v>
+        <v>1.5566</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6074000000000001</v>
+        <v>3.2653</v>
       </c>
       <c r="F15" t="n">
-        <v>0.181</v>
+        <v>-1.7087</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0308</v>
+        <v>-1.7663</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7012</v>
+        <v>-0.9477</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.732</v>
+        <v>-0.8186</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.212</v>
+        <v>0.7844</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9141</v>
+        <v>0.1745</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.1261</v>
+        <v>0.6099</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8187</v>
+        <v>-2.5507</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2128</v>
+        <v>-1.1222</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6059</v>
+        <v>-1.4285</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1887</v>
+        <v>-1.1322</v>
       </c>
       <c r="R15" t="n">
-        <v>1.887</v>
+        <v>2.2644</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9887</v>
+        <v>0.0022</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0081</v>
+        <v>-0.1225</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9806</v>
+        <v>0.1247</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8678</v>
+        <v>2.1886</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.7356</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8678</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4416</v>
+        <v>0.027</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3884</v>
+        <v>-0.0747</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9468</v>
+        <v>0.1017</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7663</v>
+        <v>-1.0308</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9477</v>
+        <v>0.7012</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8186</v>
+        <v>-1.732</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7844</v>
+        <v>-0.212</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1745</v>
+        <v>0.9141</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6099</v>
+        <v>-1.1261</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5507</v>
+        <v>-0.8187</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1222</v>
+        <v>-0.2128</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4285</v>
+        <v>-0.6059</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1322</v>
+        <v>1.6983</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1322</v>
+        <v>-0.1887</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2644</v>
+        <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1128</v>
+        <v>1.2273</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9994</v>
+        <v>0.326</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1134</v>
+        <v>0.9012</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1886</v>
+        <v>-1.8678</v>
       </c>
       <c r="W16" t="n">
-        <v>3.7356</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.547</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>E. ZOROA GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2324</v>
+        <v>-0.5119</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0299</v>
+        <v>-0.6486</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2622</v>
+        <v>0.1367</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.7687</v>
+        <v>-0.5799</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.1562</v>
+        <v>-0.0603</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.5196</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4395</v>
+        <v>-0.6284</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5629</v>
+        <v>0.0211</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1234</v>
+        <v>-0.6496</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3292</v>
+        <v>0.0485</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5934</v>
+        <v>-0.0814</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7358</v>
+        <v>0.1299</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8006</v>
+        <v>0.068</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2432</v>
+        <v>-0.0201</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5573</v>
+        <v>0.0882</v>
       </c>
       <c r="V17" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. ZOROA GARCIA</t>
+          <t>O. CAMARA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6622</v>
+        <v>-1.1319</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.746</v>
+        <v>-0.9396</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0838</v>
+        <v>-0.1922</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5799</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0603</v>
+        <v>1.0103</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5196</v>
+        <v>-0.16</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6284</v>
+        <v>1.095</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0211</v>
+        <v>0.9305</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6496</v>
+        <v>0.1645</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0485</v>
+        <v>-0.2447</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0814</v>
+        <v>0.0798</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1299</v>
+        <v>-0.3245</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0823</v>
+        <v>0.4516</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1176</v>
+        <v>0.0601</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0353</v>
+        <v>0.3916</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.8112</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. CAMARA</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3713</v>
+        <v>-1.3919</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2319</v>
+        <v>0.0555</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1393</v>
+        <v>-1.4474</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8502999999999999</v>
+        <v>-3.7687</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0103</v>
+        <v>-3.1562</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.16</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>1.095</v>
+        <v>-1.4395</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9305</v>
+        <v>-1.5629</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1645</v>
+        <v>0.1234</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2447</v>
+        <v>-2.3292</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0798</v>
+        <v>-1.5934</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3245</v>
+        <v>-0.7358</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0757</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4531</v>
+        <v>1.1322</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2122</v>
+        <v>0.641</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2323</v>
+        <v>0.2689</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4445</v>
+        <v>0.3721</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.8112</v>
+        <v>1.547</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.019</v>
+        <v>2.1696</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.7922</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-9.8424</v>
+        <v>-8.8249</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.087899999999999</v>
+        <v>-7.3084</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7546</v>
+        <v>-1.5165</v>
       </c>
       <c r="G20" t="n">
         <v>-6.9602</v>
@@ -2014,13 +2014,13 @@
         <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1839</v>
+        <v>-0.1664</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9406</v>
+        <v>-0.1611</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2433</v>
+        <v>-0.0053</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>8.282599999999997</v>
+        <v>8.282499999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>8.765700000000001</v>
+        <v>8.765599999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4830999999999994</v>
+        <v>-0.4829000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2696</v>
@@ -2077,7 +2077,7 @@
         <v>-12.8692</v>
       </c>
       <c r="N21" t="n">
-        <v>-7.567600000000001</v>
+        <v>-7.5676</v>
       </c>
       <c r="O21" t="n">
         <v>-5.3017</v>
@@ -2092,13 +2092,13 @@
         <v>17.9265</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6652</v>
+        <v>3.6651</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5078000000000001</v>
+        <v>0.5081</v>
       </c>
       <c r="U21" t="n">
-        <v>3.1572</v>
+        <v>3.1571</v>
       </c>
       <c r="V21" t="n">
         <v>2.1696</v>
